--- a/pcb/BOM.xlsx
+++ b/pcb/BOM.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="BOM_Board1_Main board_2025-08-2" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="BOM_Board1_Main board_2025-11-1" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="33">
   <si>
     <t>No.</t>
   </si>
@@ -49,7 +49,7 @@
     <t>IPCW100W13NWS1R</t>
   </si>
   <si>
-    <t>CH1,CH2,CH3,CH4,CH5,CH6</t>
+    <t>CH1,CH2,CH3,CH4,CH5,CH6,CH7,CH8</t>
   </si>
   <si>
     <t>CONN-SMD_3P-P1.00_INCP_IPCW100W13NWS1R</t>
@@ -70,6 +70,18 @@
     <t>2</t>
   </si>
   <si>
+    <t>Test-Point</t>
+  </si>
+  <si>
+    <t>KRATOS_IN</t>
+  </si>
+  <si>
+    <t>Test-Point-0.5mm</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>ESP32-S3-Zero</t>
   </si>
   <si>
@@ -82,7 +94,7 @@
     <t>C9900152785</t>
   </si>
   <si>
-    <t>3</t>
+    <t>4</t>
   </si>
   <si>
     <t>XDWF-0910-05P</t>
@@ -474,7 +486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="10" width="20" customWidth="1"/>
@@ -517,7 +529,7 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
@@ -564,52 +576,84 @@
         <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
         <v>14</v>
       </c>
       <c r="I3" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
         <v>24</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>25</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" t="s">
         <v>26</v>
-      </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" t="s">
-        <v>28</v>
       </c>
       <c r="J4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>14</v>
       </c>
     </row>
